--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136857940</v>
       </c>
       <c r="B5" t="n">
-        <v>93444</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136857940</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136857940</v>
       </c>
       <c r="B5" t="n">
-        <v>93451</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136857940</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136857940</v>
       </c>
       <c r="B5" t="n">
-        <v>93457</v>
+        <v>93470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136857940</v>
       </c>
       <c r="B5" t="n">
-        <v>93470</v>
+        <v>93471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136857940</v>
       </c>
       <c r="B5" t="n">
-        <v>93471</v>
+        <v>93474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136857940</v>
       </c>
       <c r="B5" t="n">
-        <v>93474</v>
+        <v>93484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136857940</v>
       </c>
       <c r="B5" t="n">
-        <v>93484</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136857940</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136857940</v>
       </c>
       <c r="B5" t="n">
-        <v>93490</v>
+        <v>93492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41296-2026 artfynd.xlsx
+++ b/artfynd/A 41296-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136857940</v>
       </c>
       <c r="B5" t="n">
-        <v>93492</v>
+        <v>93498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>136857958</v>
       </c>
       <c r="B6" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
